--- a/data/trans_orig/P19C05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39912</t>
+          <t>40601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66816</t>
+          <t>69164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>25485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47358</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71294</t>
+          <t>71227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107881</t>
+          <t>107222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>319486</t>
+          <t>317138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346390</t>
+          <t>345701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220929</t>
+          <t>220206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242808</t>
+          <t>242802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546709</t>
+          <t>547368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583296</t>
+          <t>583363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27434</t>
+          <t>27839</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>50433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37463</t>
+          <t>35661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79466</t>
+          <t>81360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249995</t>
+          <t>249772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>272771</t>
+          <t>272366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296102</t>
+          <t>297904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316274</t>
+          <t>316714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>554304</t>
+          <t>552410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>584072</t>
+          <t>584297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>41201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70382</t>
+          <t>68808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54151</t>
+          <t>54980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84266</t>
+          <t>84730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359885</t>
+          <t>361459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>387397</t>
+          <t>389066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117566</t>
+          <t>119240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132153</t>
+          <t>132596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>486069</t>
+          <t>485605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>516184</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135958</t>
+          <t>136119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179611</t>
+          <t>180161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65654</t>
+          <t>66732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98521</t>
+          <t>99134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210380</t>
+          <t>211741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>267197</t>
+          <t>264302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>691843</t>
+          <t>691293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>735496</t>
+          <t>735335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497728</t>
+          <t>497115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>530595</t>
+          <t>529517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1200505</t>
+          <t>1203400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1257322</t>
+          <t>1255961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>18412</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>38332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59476</t>
+          <t>57747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>90788</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83901</t>
+          <t>83784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121395</t>
+          <t>121051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209544</t>
+          <t>209595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>229530</t>
+          <t>229515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>366096</t>
+          <t>365292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396604</t>
+          <t>398333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>582612</t>
+          <t>582956</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>620106</t>
+          <t>620223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>185714</t>
+          <t>188138</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>235555</t>
+          <t>238694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>190464</t>
+          <t>186701</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242279</t>
+          <t>240093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204677</t>
+          <t>204041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211353</t>
+          <t>211352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>710061</t>
+          <t>706922</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>759902</t>
+          <t>757478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>915570</t>
+          <t>917756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>967385</t>
+          <t>971148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,88%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>299987</t>
+          <t>301232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>368962</t>
+          <t>364640</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>404658</t>
+          <t>404203</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>482617</t>
+          <t>481332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>722945</t>
+          <t>724334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>826953</t>
+          <t>827524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2079426</t>
+          <t>2083748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2148401</t>
+          <t>2147156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2257247</t>
+          <t>2258532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2335206</t>
+          <t>2335661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4361299</t>
+          <t>4360728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4465307</t>
+          <t>4463918</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33830</t>
+          <t>33977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61033</t>
+          <t>62325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33874</t>
+          <t>34660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54059</t>
+          <t>52793</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86707</t>
+          <t>88810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>334311</t>
+          <t>333019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>361514</t>
+          <t>361367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260080</t>
+          <t>259294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280265</t>
+          <t>279643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>602592</t>
+          <t>600489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>635240</t>
+          <t>636506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80270</t>
+          <t>80409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71192</t>
+          <t>71079</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111396</t>
+          <t>107755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303454</t>
+          <t>303315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>334139</t>
+          <t>335683</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>277067</t>
+          <t>276331</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296562</t>
+          <t>296110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>585829</t>
+          <t>589470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>626033</t>
+          <t>626146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63443</t>
+          <t>64943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100433</t>
+          <t>100829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41263</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70194</t>
+          <t>69303</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114123</t>
+          <t>114986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158014</t>
+          <t>161824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>435055</t>
+          <t>434659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472045</t>
+          <t>470545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170472</t>
+          <t>171363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199403</t>
+          <t>198496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>618139</t>
+          <t>614329</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662030</t>
+          <t>661167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>138167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185425</t>
+          <t>184687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75085</t>
+          <t>76786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112802</t>
+          <t>113320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228214</t>
+          <t>228332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288112</t>
+          <t>286775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>787304</t>
+          <t>788042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>835560</t>
+          <t>834562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>586125</t>
+          <t>585607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623842</t>
+          <t>622141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1383544</t>
+          <t>1384881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1443442</t>
+          <t>1443324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>61448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92287</t>
+          <t>93609</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143516</t>
+          <t>142159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185847</t>
+          <t>188213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211219</t>
+          <t>211641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>268324</t>
+          <t>266193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>311025</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342286</t>
+          <t>341864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>483976</t>
+          <t>481610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>526307</t>
+          <t>527664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>804811</t>
+          <t>806942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861916</t>
+          <t>861494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>184529</t>
+          <t>182949</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>237566</t>
+          <t>236543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>189338</t>
+          <t>193047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>247922</t>
+          <t>246180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>205500</t>
+          <t>204860</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>217211</t>
+          <t>216505</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>687819</t>
+          <t>688842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>740856</t>
+          <t>742436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898666</t>
+          <t>900408</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>957250</t>
+          <t>953541</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>396048</t>
+          <t>394576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>479844</t>
+          <t>477241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>529892</t>
+          <t>524183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>616452</t>
+          <t>614015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>947534</t>
+          <t>952000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1066624</t>
+          <t>1068701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2431956</t>
+          <t>2434559</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2515752</t>
+          <t>2517224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2525805</t>
+          <t>2528242</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2612365</t>
+          <t>2618074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4987433</t>
+          <t>4985356</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5106523</t>
+          <t>5102057</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>41539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75207</t>
+          <t>72826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345747</t>
+          <t>346261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>368491</t>
+          <t>368494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275127</t>
+          <t>274277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297119</t>
+          <t>297078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>628223</t>
+          <t>630604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>659801</t>
+          <t>661393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44897</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33126</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69573</t>
+          <t>70390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271761</t>
+          <t>271309</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294782</t>
+          <t>294486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300449</t>
+          <t>299780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319407</t>
+          <t>319841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>580659</t>
+          <t>579842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>609342</t>
+          <t>608555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>48479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78857</t>
+          <t>77840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33506</t>
+          <t>33345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68387</t>
+          <t>67902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104561</t>
+          <t>104463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326354</t>
+          <t>327371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>356094</t>
+          <t>356732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105915</t>
+          <t>106076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125940</t>
+          <t>125236</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>440072</t>
+          <t>440170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>476246</t>
+          <t>476731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86910</t>
+          <t>87419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125930</t>
+          <t>127296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>40116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68885</t>
+          <t>69626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138366</t>
+          <t>137488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186119</t>
+          <t>188801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>753575</t>
+          <t>752209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>792595</t>
+          <t>792086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>615146</t>
+          <t>614405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644121</t>
+          <t>643915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1377417</t>
+          <t>1374735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1425170</t>
+          <t>1426048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31625</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56298</t>
+          <t>55724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61294</t>
+          <t>61924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96323</t>
+          <t>96322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101049</t>
+          <t>102349</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144414</t>
+          <t>142192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368871</t>
+          <t>369445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>393544</t>
+          <t>393548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>461158</t>
+          <t>461159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>496187</t>
+          <t>495557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>838236</t>
+          <t>840458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>881601</t>
+          <t>880301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105954</t>
+          <t>103576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>149110</t>
+          <t>149747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116501</t>
+          <t>114215</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>161785</t>
+          <t>159271</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223865</t>
+          <t>222739</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236588</t>
+          <t>236554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>676179</t>
+          <t>675542</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>719335</t>
+          <t>721713</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>905052</t>
+          <t>907566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950336</t>
+          <t>952622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>254274</t>
+          <t>252651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>317619</t>
+          <t>317987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>294580</t>
+          <t>294948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>367803</t>
+          <t>366847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>566936</t>
+          <t>568321</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>664022</t>
+          <t>666142</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2338086</t>
+          <t>2337718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2401431</t>
+          <t>2403054</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2487810</t>
+          <t>2488766</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2561033</t>
+          <t>2560665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4847296</t>
+          <t>4845176</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4944382</t>
+          <t>4942997</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31335</t>
+          <t>31748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>54349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23745</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41049</t>
+          <t>42223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60038</t>
+          <t>60772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>88289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445034</t>
+          <t>444133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467147</t>
+          <t>466734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399876</t>
+          <t>398702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417180</t>
+          <t>416432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>849957</t>
+          <t>851118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879369</t>
+          <t>878635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40499</t>
+          <t>40217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66188</t>
+          <t>65618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>19209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>34916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65254</t>
+          <t>64448</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>96131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382230</t>
+          <t>382800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407919</t>
+          <t>408201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342514</t>
+          <t>342690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358617</t>
+          <t>358397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730090</t>
+          <t>729892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>760769</t>
+          <t>761575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88702</t>
+          <t>87900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>19126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34585</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>31203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>117569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>572027</t>
+          <t>572829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645212</t>
+          <t>644336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130383</t>
+          <t>130729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>145842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>708147</t>
+          <t>708128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>791126</t>
+          <t>794494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107449</t>
+          <t>105982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146544</t>
+          <t>146403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38097</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96124</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139986</t>
+          <t>142267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229644</t>
+          <t>228743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851607</t>
+          <t>851748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>890702</t>
+          <t>892169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>862745</t>
+          <t>863099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>920772</t>
+          <t>922782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1727376</t>
+          <t>1728277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1817034</t>
+          <t>1814753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28687</t>
+          <t>28932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78750</t>
+          <t>75354</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125993</t>
+          <t>124479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119472</t>
+          <t>118385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165225</t>
+          <t>168276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389010</t>
+          <t>388754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>410165</t>
+          <t>409920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>687988</t>
+          <t>689502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>735231</t>
+          <t>738627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1087608</t>
+          <t>1084557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1133361</t>
+          <t>1134448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16001</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110013</t>
+          <t>112159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143220</t>
+          <t>142811</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114048</t>
+          <t>114295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150494</t>
+          <t>151349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217211</t>
+          <t>218229</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231742</t>
+          <t>232095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>600690</t>
+          <t>601099</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>633897</t>
+          <t>631751</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>826628</t>
+          <t>825773</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>863074</t>
+          <t>862827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>243028</t>
+          <t>239773</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>356986</t>
+          <t>354544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>308800</t>
+          <t>313641</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>429117</t>
+          <t>431111</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>604277</t>
+          <t>606909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>767080</t>
+          <t>764916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2920857</t>
+          <t>2923299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3034815</t>
+          <t>3038070</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3071142</t>
+          <t>3069148</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3191459</t>
+          <t>3186618</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6011022</t>
+          <t>6013186</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6173825</t>
+          <t>6171193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>40314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69164</t>
+          <t>67497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48081</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71227</t>
+          <t>71514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107222</t>
+          <t>108443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>317138</t>
+          <t>318805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345701</t>
+          <t>345988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220206</t>
+          <t>219451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242802</t>
+          <t>242409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547368</t>
+          <t>546147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583363</t>
+          <t>583076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50433</t>
+          <t>50669</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49473</t>
+          <t>49295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81360</t>
+          <t>79723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249772</t>
+          <t>249536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>272366</t>
+          <t>272888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297904</t>
+          <t>296321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316714</t>
+          <t>315954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>552410</t>
+          <t>554047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>584297</t>
+          <t>584475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41201</t>
+          <t>41066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68808</t>
+          <t>68949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54980</t>
+          <t>54745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84730</t>
+          <t>83760</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>361459</t>
+          <t>361318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389066</t>
+          <t>389201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119240</t>
+          <t>118347</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132596</t>
+          <t>132560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>485605</t>
+          <t>486575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>515355</t>
+          <t>515590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136119</t>
+          <t>134044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180161</t>
+          <t>177388</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66732</t>
+          <t>66991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99134</t>
+          <t>99401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211741</t>
+          <t>211540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>264302</t>
+          <t>266185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>691293</t>
+          <t>694066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>735335</t>
+          <t>737410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497115</t>
+          <t>496848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>529517</t>
+          <t>529258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1203400</t>
+          <t>1201517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1255961</t>
+          <t>1256162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38332</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57747</t>
+          <t>58327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90788</t>
+          <t>90708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83784</t>
+          <t>84673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121051</t>
+          <t>123679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209595</t>
+          <t>209802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>229515</t>
+          <t>228730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365292</t>
+          <t>365372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>398333</t>
+          <t>397753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>582956</t>
+          <t>580328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>620223</t>
+          <t>619334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188138</t>
+          <t>186203</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>238694</t>
+          <t>241055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186701</t>
+          <t>189580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240093</t>
+          <t>242115</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204041</t>
+          <t>204781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211352</t>
+          <t>211350</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>706922</t>
+          <t>704561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>757478</t>
+          <t>759413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>917756</t>
+          <t>915734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>971148</t>
+          <t>968269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>301232</t>
+          <t>299802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>364640</t>
+          <t>366717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>404203</t>
+          <t>402234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>481332</t>
+          <t>482374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>724334</t>
+          <t>723635</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>827524</t>
+          <t>828223</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2083748</t>
+          <t>2081671</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2147156</t>
+          <t>2148586</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2258532</t>
+          <t>2257490</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2335661</t>
+          <t>2337630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4360728</t>
+          <t>4360029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4463918</t>
+          <t>4464617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62325</t>
+          <t>61693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34660</t>
+          <t>35304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>52672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88810</t>
+          <t>86404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>333019</t>
+          <t>333651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>361367</t>
+          <t>362166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259294</t>
+          <t>258650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279643</t>
+          <t>278853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>600489</t>
+          <t>602895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>636506</t>
+          <t>636627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48041</t>
+          <t>48499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80409</t>
+          <t>79962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37170</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71079</t>
+          <t>69601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107755</t>
+          <t>111037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303315</t>
+          <t>303762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335683</t>
+          <t>335225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>276331</t>
+          <t>276144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296110</t>
+          <t>296456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>589470</t>
+          <t>586188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>626146</t>
+          <t>627624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64943</t>
+          <t>65161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100829</t>
+          <t>100049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42170</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69303</t>
+          <t>68674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,47 +4104,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>135997</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>115399</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>158414</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>17,52%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>135997</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>114986</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>161824</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>434659</t>
+          <t>435439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470545</t>
+          <t>470327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171363</t>
+          <t>171992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>198496</t>
+          <t>199471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,47 +4217,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>82,88%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>640156</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>617739</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>660754</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>82,48%</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>640156</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>614329</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>661167</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>82,48%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138167</t>
+          <t>139692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184687</t>
+          <t>184926</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76786</t>
+          <t>77799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113320</t>
+          <t>116267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228332</t>
+          <t>226367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286775</t>
+          <t>288526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>788042</t>
+          <t>787803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>834562</t>
+          <t>833037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>585607</t>
+          <t>582660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>622141</t>
+          <t>621128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1384881</t>
+          <t>1383130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1443324</t>
+          <t>1445289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61448</t>
+          <t>61549</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93609</t>
+          <t>94082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142159</t>
+          <t>143009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188213</t>
+          <t>189826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211641</t>
+          <t>214343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266193</t>
+          <t>267669</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309703</t>
+          <t>309230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341864</t>
+          <t>341763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>481610</t>
+          <t>479997</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>527664</t>
+          <t>526814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>806942</t>
+          <t>805466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861494</t>
+          <t>858792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>182949</t>
+          <t>184262</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>236543</t>
+          <t>239009</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>193047</t>
+          <t>191364</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>246180</t>
+          <t>245520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204860</t>
+          <t>205557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216505</t>
+          <t>216548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>688842</t>
+          <t>686376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>742436</t>
+          <t>741123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>900408</t>
+          <t>901068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>953541</t>
+          <t>955224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>394576</t>
+          <t>393451</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>477241</t>
+          <t>478079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>524183</t>
+          <t>529692</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>614015</t>
+          <t>617949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>952000</t>
+          <t>944871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1068701</t>
+          <t>1064025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2434559</t>
+          <t>2433721</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2517224</t>
+          <t>2518349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2528242</t>
+          <t>2524308</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2618074</t>
+          <t>2612565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4985356</t>
+          <t>4990032</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5102057</t>
+          <t>5109186</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>19036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41353</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18738</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41539</t>
+          <t>42401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42037</t>
+          <t>43734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72826</t>
+          <t>74763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>346261</t>
+          <t>345822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>368494</t>
+          <t>368578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274277</t>
+          <t>273415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297078</t>
+          <t>296458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630604</t>
+          <t>628667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>661393</t>
+          <t>659696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>22926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45349</t>
+          <t>46076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>33344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41677</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70390</t>
+          <t>71537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271309</t>
+          <t>270582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294486</t>
+          <t>293732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299780</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319841</t>
+          <t>319658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579842</t>
+          <t>578695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>608555</t>
+          <t>609108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>48663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77840</t>
+          <t>78614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33345</t>
+          <t>32911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67902</t>
+          <t>67783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104463</t>
+          <t>103204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327371</t>
+          <t>326597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>356732</t>
+          <t>356548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106076</t>
+          <t>106510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125236</t>
+          <t>125720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>440170</t>
+          <t>441429</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>476731</t>
+          <t>476850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87419</t>
+          <t>87148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127296</t>
+          <t>127187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69626</t>
+          <t>68271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137488</t>
+          <t>135640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188801</t>
+          <t>184574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>752209</t>
+          <t>752318</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>792086</t>
+          <t>792357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>614405</t>
+          <t>615760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643915</t>
+          <t>644690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1374735</t>
+          <t>1378962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1426048</t>
+          <t>1427896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31621</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55724</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61924</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96322</t>
+          <t>97130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102349</t>
+          <t>101001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142192</t>
+          <t>143240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369445</t>
+          <t>368810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>393548</t>
+          <t>393980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>461159</t>
+          <t>460351</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495557</t>
+          <t>494727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>840458</t>
+          <t>839410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>880301</t>
+          <t>881649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103576</t>
+          <t>106807</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>149747</t>
+          <t>150721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114215</t>
+          <t>114462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>159271</t>
+          <t>160861</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222739</t>
+          <t>223658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236554</t>
+          <t>236733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>675542</t>
+          <t>674568</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>721713</t>
+          <t>718482</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>907566</t>
+          <t>905976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>952622</t>
+          <t>952375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>252651</t>
+          <t>251618</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>317987</t>
+          <t>315755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>294948</t>
+          <t>296792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>366847</t>
+          <t>370391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>568321</t>
+          <t>565712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>666142</t>
+          <t>663954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2337718</t>
+          <t>2339950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2403054</t>
+          <t>2404087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2488766</t>
+          <t>2485222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2560665</t>
+          <t>2558821</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4845176</t>
+          <t>4847364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4942997</t>
+          <t>4945606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>45849</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31748</t>
+          <t>35301</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54349</t>
+          <t>58606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32091</t>
+          <t>34393</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>73484</t>
+          <t>80242</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60772</t>
+          <t>66438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88289</t>
+          <t>96354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>457088</t>
+          <t>495414</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444133</t>
+          <t>482657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466734</t>
+          <t>505962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>408834</t>
+          <t>446934</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>398702</t>
+          <t>436788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>416432</t>
+          <t>454717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>865923</t>
+          <t>942348</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>851118</t>
+          <t>926236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>878635</t>
+          <t>956152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51961</t>
+          <t>54945</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40217</t>
+          <t>42986</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65618</t>
+          <t>68768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34916</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>78601</t>
+          <t>83970</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64448</t>
+          <t>68890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96131</t>
+          <t>100658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>396457</t>
+          <t>424387</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382800</t>
+          <t>410564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408201</t>
+          <t>436346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>350966</t>
+          <t>388895</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342690</t>
+          <t>379546</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358397</t>
+          <t>396575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>747422</t>
+          <t>813283</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729892</t>
+          <t>796595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>761575</t>
+          <t>828363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51341</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16393</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87900</t>
+          <t>69611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>77621</t>
+          <t>85507</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>70524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117569</t>
+          <t>102982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>609388</t>
+          <t>407959</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>572829</t>
+          <t>394254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644336</t>
+          <t>420256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>138689</t>
+          <t>155232</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130729</t>
+          <t>145217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145842</t>
+          <t>162524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>748076</t>
+          <t>563191</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>708128</t>
+          <t>545716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>794494</t>
+          <t>578174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>125147</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105982</t>
+          <t>122032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146403</t>
+          <t>165538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71340</t>
+          <t>77870</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>65301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95770</t>
+          <t>91879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>196487</t>
+          <t>219864</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142267</t>
+          <t>193548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>228743</t>
+          <t>245368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>873004</t>
+          <t>953705</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>851748</t>
+          <t>930161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892169</t>
+          <t>973667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>887529</t>
+          <t>758920</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>863099</t>
+          <t>744911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>922782</t>
+          <t>771489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1760533</t>
+          <t>1712625</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1728277</t>
+          <t>1687121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1814753</t>
+          <t>1738941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28932</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50098</t>
+          <t>52721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>105788</t>
+          <t>116533</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75354</t>
+          <t>101927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124479</t>
+          <t>133397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>144581</t>
+          <t>157362</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118385</t>
+          <t>138378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168276</t>
+          <t>179191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>400058</t>
+          <t>469018</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>388754</t>
+          <t>457127</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409920</t>
+          <t>478653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>708193</t>
+          <t>676972</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>689502</t>
+          <t>660108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>738627</t>
+          <t>691578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1108252</t>
+          <t>1145991</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1084557</t>
+          <t>1124162</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1134448</t>
+          <t>1164975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>138641</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112159</t>
+          <t>121839</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142811</t>
+          <t>157002</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>131533</t>
+          <t>144375</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114295</t>
+          <t>127219</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151349</t>
+          <t>166325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>227752</t>
+          <t>220052</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218229</t>
+          <t>209533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232095</t>
+          <t>224278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>617836</t>
+          <t>680101</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>601099</t>
+          <t>661740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>631751</t>
+          <t>696903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>845589</t>
+          <t>900154</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>825773</t>
+          <t>878204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>862827</t>
+          <t>917310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>314097</t>
+          <t>345259</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>239773</t>
+          <t>312967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>354544</t>
+          <t>382871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>388211</t>
+          <t>426063</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>313641</t>
+          <t>396192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>431111</t>
+          <t>456931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>702308</t>
+          <t>771321</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>606909</t>
+          <t>726442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>764916</t>
+          <t>818958</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2963746</t>
+          <t>2970536</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2923299</t>
+          <t>2932924</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3038070</t>
+          <t>3002828</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3112048</t>
+          <t>3107055</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3069148</t>
+          <t>3076187</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3186618</t>
+          <t>3136926</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6075794</t>
+          <t>6077592</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6013186</t>
+          <t>6029955</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6171193</t>
+          <t>6122471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
